--- a/naver-place-crawler/results_health/전주_PT.xlsx
+++ b/naver-place-crawler/results_health/전주_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북특별자치도 전주시 덕진구 솔내로 131 4층 401,402호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w23okib</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="Q3" t="n">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="R3" t="n">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 모악로 4678 7층</t>
+          <t>전북특별자치도 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +798,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwx54rl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -824,10 +816,10 @@
         <v>464</v>
       </c>
       <c r="Q4" t="n">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="R4" t="n">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -875,7 +867,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 시천로 35 용진빌딩 5층</t>
+          <t>전북특별자치도 전주시 덕진구 시천로 35 용진빌딩 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +892,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wws0fj1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q5" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="R5" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -973,7 +961,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 세병2길 25 . 5층 501호 5층 핑크팬더즈</t>
+          <t>전북특별자치도 전주시 덕진구 세병2길 25 . 5층 501호 5층 핑크팬더즈</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +986,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43e8k</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,10 +1001,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q6" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="R6" t="n">
         <v>1098</v>
@@ -1054,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>핑크팬더즈 삼천평화점 헬스&amp;PT</t>
+          <t>리브리드 효자점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pinkpandazym@naver.com</t>
+          <t>welcomerebreed@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1351-9679</t>
+          <t>0507-1368-8931</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
+          <t>전북특별자치도 전주시 완산구 홍산중앙로 13 돌핀빌딩 201호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_pinkpandaz</t>
+          <t>https://blog.naver.com/welcomerebreed</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,19 +1075,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44lxq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,17 +1091,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>740</v>
+        <v>396</v>
       </c>
       <c r="Q7" t="n">
-        <v>630</v>
+        <v>227</v>
       </c>
       <c r="R7" t="n">
-        <v>1370</v>
+        <v>623</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1302096727</t>
+          <t>2088657732</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302096727</t>
+          <t>https://m.place.naver.com/place/2088657732</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1161,15 +1141,11 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1337-8203</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 화암4길 60 4층</t>
+          <t>전북특별자치도 전주시 덕진구 화암4길 60 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwzxui7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q8" t="n">
         <v>343</v>
       </c>
       <c r="R8" t="n">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1250,25 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>24시 헬스 PT 제로백피트니스 효자점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1399-8873</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북특별자치도 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>https://blog.naver.com/zeroback2022/223179008503</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,19 +1259,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>248</v>
+        <v>1231</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>402</v>
       </c>
       <c r="R9" t="n">
-        <v>275</v>
+        <v>1633</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>1709963411</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/1709963411</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>온탑피트니스 만성점</t>
+          <t>MK휘트니스 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ontopfit@naver.com</t>
+          <t>ggomaelf@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1355-5810</t>
+          <t>0507-1315-7750</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+          <t>전북특별자치도 전주시 완산구 석산1길 16 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ontopfit</t>
+          <t>https://www.instagram.com/mk_jeonju</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,19 +1353,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4egfn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q10" t="n">
-        <v>281</v>
+        <v>67</v>
       </c>
       <c r="R10" t="n">
-        <v>456</v>
+        <v>241</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1089561368</t>
+          <t>1420068659</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089561368</t>
+          <t>https://m.place.naver.com/place/1420068659</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,29 +1410,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>하이짐 헬스&amp;PT 평화점</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>higym_official@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1375-7398</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북특별자치도 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym_official</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1443,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1499,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="Q11" t="n">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2060819661</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060819661</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1536,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>사람휘트니스 서신16호점</t>
+          <t>온탑피트니스 만성점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hoy04245@naver.com</t>
+          <t>ontopfit@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1412-6116</t>
+          <t>0507-1355-5810</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 서신로 62 지리산빌딩 5층</t>
+          <t>전북특별자치도 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/saramfitness_seosin</t>
+          <t>https://blog.naver.com/ontopfit</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1573,19 +1537,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5z5kr</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1597,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="Q12" t="n">
-        <v>123</v>
+        <v>281</v>
       </c>
       <c r="R12" t="n">
-        <v>219</v>
+        <v>456</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,12 +1572,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1974601302</t>
+          <t>1089561368</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1974601302</t>
+          <t>https://m.place.naver.com/place/1089561368</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/전주_PT.xlsx
+++ b/naver-place-crawler/results_health/전주_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>필라테스해</t>
+          <t>짐플릭스 송천점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wjdalgo23@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1352-1212</t>
+          <t>0507-1382-8094</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 백제대로 295 3층 302호 필라테스 해</t>
+          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lilly_jung___</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5unak</t>
+          <t>https://talk.naver.com/ct/w23okib</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>94</v>
+        <v>625</v>
       </c>
       <c r="Q2" t="n">
-        <v>87</v>
+        <v>860</v>
       </c>
       <c r="R2" t="n">
-        <v>181</v>
+        <v>1485</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1481141593</t>
+          <t>1027880481</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1481141593</t>
+          <t>https://m.place.naver.com/place/1027880481</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐플릭스 송천점</t>
+          <t>짐플릭스 평화점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -673,18 +673,18 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1382-8094</t>
+          <t>0507-1408-8909</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wwx54rl</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>621</v>
+        <v>479</v>
       </c>
       <c r="Q3" t="n">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="R3" t="n">
-        <v>1495</v>
+        <v>1361</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1027880481</t>
+          <t>1336256244</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027880481</t>
+          <t>https://m.place.naver.com/place/1336256244</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>짐플릭스 평화점</t>
+          <t>짐플릭스 송천2호점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -767,18 +771,18 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1408-8909</t>
+          <t>0507-1484-8094</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 완산구 모악로 4678 7층</t>
+          <t>전북 전주시 덕진구 시천로 35 용진빌딩 5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr/</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -798,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wws0fj1</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>464</v>
+        <v>142</v>
       </c>
       <c r="Q4" t="n">
-        <v>896</v>
+        <v>572</v>
       </c>
       <c r="R4" t="n">
-        <v>1360</v>
+        <v>714</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1336256244</t>
+          <t>2051918606</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336256244</t>
+          <t>https://m.place.naver.com/place/2051918606</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -850,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>짐플릭스 송천2호점</t>
+          <t>핑크팬더즈 삼천평화점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gymflix063@naver.com</t>
+          <t>pinkpandazym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1484-8094</t>
+          <t>0507-1351-9679</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 덕진구 시천로 35 용진빌딩 5층</t>
+          <t>전북 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://www.instagram.com/_pinkpandaz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -892,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44lxq</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>136</v>
+        <v>743</v>
       </c>
       <c r="Q5" t="n">
-        <v>565</v>
+        <v>628</v>
       </c>
       <c r="R5" t="n">
-        <v>701</v>
+        <v>1371</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2051918606</t>
+          <t>1302096727</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051918606</t>
+          <t>https://m.place.naver.com/place/1302096727</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -944,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>핑크팬더즈 에코송천점 헬스&amp;PT&amp;필라테스</t>
+          <t>리브리드 효자점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pinkpandaz3@naver.com</t>
+          <t>welcomerebreed@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1340-9679</t>
+          <t>0507-1368-8931</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 덕진구 세병2길 25 . 5층 501호 5층 핑크팬더즈</t>
+          <t>전북 전주시 완산구 홍산중앙로 13 돌핀빌딩 201호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pinkpandaz3</t>
+          <t>https://blog.naver.com/welcomerebreed</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfasqmq</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,17 +1013,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>428</v>
+        <v>405</v>
       </c>
       <c r="Q6" t="n">
-        <v>670</v>
+        <v>233</v>
       </c>
       <c r="R6" t="n">
-        <v>1098</v>
+        <v>638</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1899908556</t>
+          <t>2088657732</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1899908556</t>
+          <t>https://m.place.naver.com/place/2088657732</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>리브리드 효자점</t>
+          <t>카이로짐 체형관리 PT샵 효천점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>welcomerebreed@naver.com</t>
+          <t>hyesungda@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1368-8931</t>
+          <t>0507-1415-5022</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 완산구 홍산중앙로 13 돌핀빌딩 201호</t>
+          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/welcomerebreed</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,20 +1086,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ftdy</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>396</v>
+        <v>68</v>
       </c>
       <c r="Q7" t="n">
-        <v>227</v>
+        <v>76</v>
       </c>
       <c r="R7" t="n">
-        <v>623</v>
+        <v>144</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2088657732</t>
+          <t>1693804133</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2088657732</t>
+          <t>https://m.place.naver.com/place/1693804133</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1152,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>onewayeco@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1145,12 +1165,12 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 덕진구 화암4길 60 4층</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onewayfitness3</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1170,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1292</v>
+        <v>253</v>
       </c>
       <c r="Q8" t="n">
-        <v>343</v>
+        <v>27</v>
       </c>
       <c r="R8" t="n">
-        <v>1635</v>
+        <v>280</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1857733969</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857733969</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 효자점</t>
+          <t>하이짐 헬스&amp;PT 평화점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>higym_official@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1399-8873</t>
+          <t>0507-1375-7398</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
+          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223179008503</t>
+          <t>https://blog.naver.com/higym_official</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1231</v>
+        <v>216</v>
       </c>
       <c r="Q9" t="n">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="R9" t="n">
-        <v>1633</v>
+        <v>295</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1709963411</t>
+          <t>2060819661</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709963411</t>
+          <t>https://m.place.naver.com/place/2060819661</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MK휘트니스 헬스&amp;PT 효자점</t>
+          <t>온탑피트니스 만성점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ggomaelf@naver.com</t>
+          <t>ontopfit@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1315-7750</t>
+          <t>0507-1355-5810</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 완산구 석산1길 16 3층</t>
+          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mk_jeonju</t>
+          <t>https://blog.naver.com/ontopfit</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,15 +1377,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4egfn</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q10" t="n">
-        <v>67</v>
+        <v>280</v>
       </c>
       <c r="R10" t="n">
-        <v>241</v>
+        <v>455</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,201 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1420068659</t>
+          <t>1089561368</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420068659</t>
+          <t>https://m.place.naver.com/place/1089561368</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>brewgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>전북특별자치도 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>249</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>27</v>
-      </c>
-      <c r="R11" t="n">
-        <v>276</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2009027135</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>온탑피트니스 만성점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ontopfit@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1355-5810</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>전북특별자치도 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/ontopfit</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>175</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>281</v>
-      </c>
-      <c r="R12" t="n">
-        <v>456</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1089561368</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1089561368</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/전주_PT.xlsx
+++ b/naver-place-crawler/results_health/전주_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="Q2" t="n">
         <v>860</v>
       </c>
       <c r="R2" t="n">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q4" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="R4" t="n">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="Q5" t="n">
         <v>628</v>
       </c>
       <c r="R5" t="n">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q6" t="n">
         <v>233</v>
       </c>
       <c r="R6" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,41 +1042,37 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>카이로짐 체형관리 PT샵 효천점</t>
+          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hyesungda@naver.com</t>
+          <t>onewayeco@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1415-5022</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
+          <t>전북 전주시 덕진구 화암4길 60 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/onewayfitness3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,7 +1082,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ftdy</t>
+          <t>https://talk.naver.com/ct/wwzxui7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1107,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>68</v>
+        <v>1305</v>
       </c>
       <c r="Q7" t="n">
-        <v>76</v>
+        <v>331</v>
       </c>
       <c r="R7" t="n">
-        <v>144</v>
+        <v>1636</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,47 +1126,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1693804133</t>
+          <t>1857733969</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693804133</t>
+          <t>https://m.place.naver.com/place/1857733969</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>카이로짐 체형관리 PT샵 효천점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>hyesungda@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1415-5022</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
+          <t>https://talk.naver.com/ct/w4ftdy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>253</v>
+        <v>68</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="R8" t="n">
-        <v>280</v>
+        <v>144</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>1693804133</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/1693804133</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1246,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>하이짐 헬스&amp;PT 평화점</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>higym_official@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1375-7398</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym_official</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,15 +1279,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="Q9" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2060819661</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060819661</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,101 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>하이짐 헬스&amp;PT 평화점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>higym_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1375-7398</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/higym_official</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>79</v>
+      </c>
+      <c r="R11" t="n">
+        <v>298</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2060819661</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2060819661</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/전주_PT.xlsx
+++ b/naver-place-crawler/results_health/전주_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북특별자치도 전주시 덕진구 솔내로 131 4층 401,402호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w23okib</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 모악로 4678 7층</t>
+          <t>전북특별자치도 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwx54rl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 시천로 35 용진빌딩 5층</t>
+          <t>전북특별자치도 전주시 덕진구 시천로 35 용진빌딩 5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wws0fj1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
+          <t>전북특별자치도 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44lxq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산중앙로 13 돌핀빌딩 201호</t>
+          <t>전북특별자치도 전주시 완산구 홍산중앙로 13 돌핀빌딩 201호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wfasqmq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1067,7 +1047,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 화암4길 60 4층</t>
+          <t>전북특별자치도 전주시 덕진구 화암4길 60 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1092,14 +1072,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwzxui7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1165,7 +1141,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
+          <t>전북특별자치도 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,14 +1166,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ftdy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1259,7 +1231,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북특별자치도 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1284,14 +1256,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1357,7 +1325,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+          <t>전북특별자치도 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1382,14 +1350,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4egfn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1455,7 +1419,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북특별자치도 전주시 완산구 평화18길 29 4층 하이짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1486,7 +1450,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">

--- a/naver-place-crawler/results_health/전주_PT.xlsx
+++ b/naver-place-crawler/results_health/전주_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>짐플릭스 송천점</t>
+          <t>짐플릭스 평화점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -575,18 +575,18 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1382-8094</t>
+          <t>0507-1408-8909</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wwx54rl</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>627</v>
+        <v>479</v>
       </c>
       <c r="Q2" t="n">
-        <v>860</v>
+        <v>882</v>
       </c>
       <c r="R2" t="n">
-        <v>1487</v>
+        <v>1361</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1027880481</t>
+          <t>1336256244</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027880481</t>
+          <t>https://m.place.naver.com/place/1336256244</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,7 +662,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐플릭스 평화점</t>
+          <t>짐플릭스 송천점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,18 +673,18 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1408-8909</t>
+          <t>0507-1382-8094</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 완산구 모악로 4678 7층</t>
+          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr/</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w23okib</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>479</v>
+        <v>627</v>
       </c>
       <c r="Q3" t="n">
-        <v>882</v>
+        <v>860</v>
       </c>
       <c r="R3" t="n">
-        <v>1361</v>
+        <v>1487</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1336256244</t>
+          <t>1027880481</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336256244</t>
+          <t>https://m.place.naver.com/place/1027880481</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 덕진구 시천로 35 용진빌딩 5층</t>
+          <t>전북 전주시 덕진구 시천로 35 용진빌딩 5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wws0fj1</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
+          <t>전북 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44lxq</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="Q5" t="n">
         <v>628</v>
       </c>
       <c r="R5" t="n">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 완산구 홍산중앙로 13 돌핀빌딩 201호</t>
+          <t>전북 전주시 완산구 홍산중앙로 13 돌핀빌딩 201호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfasqmq</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q6" t="n">
         <v>233</v>
       </c>
       <c r="R6" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1047,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 덕진구 화암4길 60 4층</t>
+          <t>전북 전주시 덕진구 화암4길 60 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1072,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wwzxui7</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1141,7 +1165,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
+          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1166,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ftdy</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1231,7 +1259,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1256,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1271,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q9" t="n">
         <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1325,7 +1357,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1350,10 +1382,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4egfn</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1419,7 +1455,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북특별자치도 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1450,7 +1486,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1459,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q11" t="n">
         <v>79</v>
       </c>
       <c r="R11" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/전주_PT.xlsx
+++ b/naver-place-crawler/results_health/전주_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V189"/>
+  <dimension ref="A1:V202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18136,6 +18136,1228 @@
         </is>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>바디포커스 운동&amp;재활센터 LH점</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>huswl1214@naver.com</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>0507-1305-8931</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 완산구 호암로 84 3층 바디포커스 LH점</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/huswl1214/223893338680</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>63</v>
+      </c>
+      <c r="R190" t="n">
+        <v>100</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>1813815685</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1813815685</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>모이라짐 신시가지점</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>moiragym@naver.com</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>0507-1498-9102</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 완산구 홍산중앙로 18 7층</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/moiragym</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>174</v>
+      </c>
+      <c r="R191" t="n">
+        <v>186</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>36960147</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36960147</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>스포츠센터</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>좋음PT</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>kkk43211@naver.com</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>themosttimes@tmt.co.kr</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>063-223-8231</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 완산구 강변로 70 로드빌딩2층 좋음PT</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://www.themosttimes.co.kr/43119</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>308</v>
+      </c>
+      <c r="R192" t="n">
+        <v>459</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>1582951760</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1582951760</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>제로백 PT 반월 7호점</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>zeroback2022@naver.com</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>0507-1382-0125</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 덕진구 쪽구름로 124 4층 제로백피트니스</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/zeroback2022/223821074759</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>2</v>
+      </c>
+      <c r="R193" t="n">
+        <v>7</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>2082432764</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2082432764</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>24시 헬스 PT 제로백피트니스 반월점</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>zeroback2022@naver.com</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>0507-1438-8873</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 덕진구 쪽구름로 124 4층 401호</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/zeroback2022/223794709810</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>492</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>73</v>
+      </c>
+      <c r="R194" t="n">
+        <v>565</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>1691197101</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1691197101</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>온탑피트니스 만성점</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ontopfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>0507-1355-5810</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ontopfit</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>280</v>
+      </c>
+      <c r="R195" t="n">
+        <v>455</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>1089561368</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1089561368</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>무예,격투기</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>퍼스트짐 서신본관</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>z1x2a3s4@naver.com</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>0507-1401-3222</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 완산구 새터로 52-7 광진장미아파트 상가2층</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>http://instagram.com/firstgym_jiujitsu</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>106</v>
+      </c>
+      <c r="R196" t="n">
+        <v>116</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>1616064720</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1616064720</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>헬스챌린저</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>rkdgml1817@naver.com</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 덕진구 백제대로 555 B1층 헬스챌린저</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rkdgml1817</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>21</v>
+      </c>
+      <c r="R197" t="n">
+        <v>33</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>1642194859</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1642194859</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>골드피티짐</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>superwoo1@naver.com</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>070-7869-9976</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 덕진구 조경단로 33-1 2층</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>291</v>
+      </c>
+      <c r="R198" t="n">
+        <v>291</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>20662679</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20662679</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>뷰티니스짐 효자지점</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>beautinessgymhyoja@naver.com</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>0507-1327-9682</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 완산구 효동2길 1 4층</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/beautinessgymhyoja</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>1960</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>79</v>
+      </c>
+      <c r="R199" t="n">
+        <v>2039</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>1129813754</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1129813754</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>베가짐</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>bjk7300@naver.com</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>0507-1460-7930</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 완산구 서신로 5 지하1층</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vegagym_official_</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>5</v>
+      </c>
+      <c r="R200" t="n">
+        <v>31</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>2087401469</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2087401469</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>국가대표휘트니스</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>pkmpowere@naver.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>0507-1388-1154</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 덕진구 안덕원로 276 2동 3층</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kyeongmo.park</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>1196</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>56</v>
+      </c>
+      <c r="R201" t="n">
+        <v>1252</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>1276713609</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1276713609</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>바디플랜짐</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>plangym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>0507-1369-8691</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>전북특별자치도 전주시 완산구 여울로 35 7층 바디플랜짐</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodyplan_gym</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>160</v>
+      </c>
+      <c r="R202" t="n">
+        <v>174</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>1945263108</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1945263108</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver-place-crawler/results_health/전주_PT.xlsx
+++ b/naver-place-crawler/results_health/전주_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -1049,34 +1049,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>카이로짐 체형관리 PT샵 효천점</t>
+          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hyesungda@naver.com</t>
+          <t>onewayeco@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1415-5022</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
+          <t>전북 전주시 덕진구 화암4길 60 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/onewayfitness3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,7 +1082,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ftdy</t>
+          <t>https://talk.naver.com/ct/wwzxui7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1107,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>68</v>
+        <v>1305</v>
       </c>
       <c r="Q7" t="n">
-        <v>76</v>
+        <v>331</v>
       </c>
       <c r="R7" t="n">
-        <v>144</v>
+        <v>1636</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1693804133</t>
+          <t>1857733969</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693804133</t>
+          <t>https://m.place.naver.com/place/1857733969</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1147,30 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>카이로짐 체형관리 PT샵 효천점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>hyesungda@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1415-5022</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
+          <t>https://talk.naver.com/ct/w4ftdy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>261</v>
+        <v>68</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="R8" t="n">
-        <v>288</v>
+        <v>144</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>1693804133</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/1693804133</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,29 +1246,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>하이짐 헬스&amp;PT 평화점</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>higym_official@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1375-7398</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym_official</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,18 +1279,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>222</v>
+        <v>261</v>
       </c>
       <c r="Q9" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2060819661</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060819661</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>온탑피트니스 만성점</t>
+          <t>하이짐 헬스&amp;PT 평화점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ontopfit@naver.com</t>
+          <t>higym_official@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1355-5810</t>
+          <t>0507-1375-7398</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ontopfit</t>
+          <t>https://blog.naver.com/higym_official</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1382,17 +1382,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4egfn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="Q10" t="n">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="R10" t="n">
-        <v>455</v>
+        <v>301</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1089561368</t>
+          <t>2060819661</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089561368</t>
+          <t>https://m.place.naver.com/place/2060819661</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,29 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>사람휘트니스 서신16호점</t>
+          <t>온탑피트니스 만성점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hoy04245@naver.com</t>
+          <t>ontopfit@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1412-6116</t>
+          <t>0507-1355-5810</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 서신로 62 지리산빌딩 5층</t>
+          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/saramfitness_seosin</t>
+          <t>https://blog.naver.com/ontopfit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1475,7 +1471,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5z5kr</t>
+          <t>https://talk.naver.com/ct/w4egfn</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="Q11" t="n">
-        <v>123</v>
+        <v>280</v>
       </c>
       <c r="R11" t="n">
-        <v>219</v>
+        <v>455</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1974601302</t>
+          <t>1089561368</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1974601302</t>
+          <t>https://m.place.naver.com/place/1089561368</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/전주_PT.xlsx
+++ b/naver-place-crawler/results_health/전주_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -628,10 +628,10 @@
         <v>479</v>
       </c>
       <c r="Q2" t="n">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="R2" t="n">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="Q3" t="n">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="R3" t="n">
-        <v>1486</v>
+        <v>1496</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -760,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>짐플릭스 송천2호점</t>
+          <t>핑크팬더즈 삼천평화점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gymflix063@naver.com</t>
+          <t>pinkpandazym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1484-8094</t>
+          <t>0507-1351-9679</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 시천로 35 용진빌딩 5층</t>
+          <t>전북 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://www.instagram.com/_pinkpandaz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wws0fj1</t>
+          <t>https://talk.naver.com/ct/w44lxq</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>146</v>
+        <v>745</v>
       </c>
       <c r="Q4" t="n">
-        <v>574</v>
+        <v>629</v>
       </c>
       <c r="R4" t="n">
-        <v>720</v>
+        <v>1374</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2051918606</t>
+          <t>1302096727</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051918606</t>
+          <t>https://m.place.naver.com/place/1302096727</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>핑크팬더즈 삼천평화점 헬스&amp;PT</t>
+          <t>짐플릭스 송천2호점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pinkpandazym@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1351-9679</t>
+          <t>0507-1484-8094</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
+          <t>전북 전주시 덕진구 시천로 35 용진빌딩 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_pinkpandaz</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44lxq</t>
+          <t>https://talk.naver.com/ct/wws0fj1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>745</v>
+        <v>147</v>
       </c>
       <c r="Q5" t="n">
-        <v>628</v>
+        <v>574</v>
       </c>
       <c r="R5" t="n">
-        <v>1373</v>
+        <v>721</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1302096727</t>
+          <t>2051918606</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302096727</t>
+          <t>https://m.place.naver.com/place/2051918606</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1020,10 +1020,10 @@
         <v>409</v>
       </c>
       <c r="Q6" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R6" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1054,25 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
+          <t>24시 헬스 PT 제로백피트니스 효자점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>onewayeco@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1399-8873</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 화암4길 60 4층</t>
+          <t>전북 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onewayfitness3</t>
+          <t>https://blog.naver.com/zeroback2022/223179008503</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwzxui7</t>
+          <t>https://talk.naver.com/ct/w5ycz5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1305</v>
+        <v>1254</v>
       </c>
       <c r="Q7" t="n">
-        <v>331</v>
+        <v>423</v>
       </c>
       <c r="R7" t="n">
-        <v>1636</v>
+        <v>1677</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1857733969</t>
+          <t>1709963411</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857733969</t>
+          <t>https://m.place.naver.com/place/1709963411</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1303,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q9" t="n">
         <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q10" t="n">
         <v>79</v>
       </c>
       <c r="R10" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1495,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q11" t="n">
         <v>280</v>
       </c>
       <c r="R11" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/전주_PT.xlsx
+++ b/naver-place-crawler/results_health/전주_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,39 +564,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>짐플릭스 평화점</t>
+          <t>카이로짐 체형관리 PT샵 효천점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gymflix063@naver.com</t>
+          <t>hyesungda@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1408-8909</t>
+          <t>0507-1415-5022</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 모악로 4678 7층</t>
+          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwx54rl</t>
+          <t>https://talk.naver.com/ct/w4ftdy</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>479</v>
+        <v>68</v>
       </c>
       <c r="Q2" t="n">
-        <v>884</v>
+        <v>76</v>
       </c>
       <c r="R2" t="n">
-        <v>1363</v>
+        <v>144</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1336256244</t>
+          <t>1693804133</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336256244</t>
+          <t>https://m.place.naver.com/place/1693804133</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐플릭스 송천점</t>
+          <t>짐플릭스 평화점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -673,18 +673,18 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1382-8094</t>
+          <t>0507-1408-8909</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w23okib</t>
+          <t>https://talk.naver.com/ct/wwx54rl</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>635</v>
+        <v>480</v>
       </c>
       <c r="Q3" t="n">
-        <v>861</v>
+        <v>884</v>
       </c>
       <c r="R3" t="n">
-        <v>1496</v>
+        <v>1364</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1027880481</t>
+          <t>1336256244</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027880481</t>
+          <t>https://m.place.naver.com/place/1336256244</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -760,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>핑크팬더즈 삼천평화점 헬스&amp;PT</t>
+          <t>짐플릭스 송천점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pinkpandazym@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1351-9679</t>
+          <t>0507-1382-8094</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
+          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_pinkpandaz</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44lxq</t>
+          <t>https://talk.naver.com/ct/w23okib</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>745</v>
+        <v>639</v>
       </c>
       <c r="Q4" t="n">
-        <v>629</v>
+        <v>862</v>
       </c>
       <c r="R4" t="n">
-        <v>1374</v>
+        <v>1501</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1302096727</t>
+          <t>1027880481</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302096727</t>
+          <t>https://m.place.naver.com/place/1027880481</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -858,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>짐플릭스 송천2호점</t>
+          <t>핑크팬더즈 삼천평화점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gymflix063@naver.com</t>
+          <t>pinkpandazym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1484-8094</t>
+          <t>0507-1351-9679</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 시천로 35 용진빌딩 5층</t>
+          <t>전북 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://www.instagram.com/_pinkpandaz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wws0fj1</t>
+          <t>https://talk.naver.com/ct/w44lxq</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>147</v>
+        <v>745</v>
       </c>
       <c r="Q5" t="n">
-        <v>574</v>
+        <v>629</v>
       </c>
       <c r="R5" t="n">
-        <v>721</v>
+        <v>1374</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2051918606</t>
+          <t>1302096727</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051918606</t>
+          <t>https://m.place.naver.com/place/1302096727</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리브리드 효자점</t>
+          <t>짐플릭스 송천2호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>welcomerebreed@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1368-8931</t>
+          <t>0507-1484-8094</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산중앙로 13 돌핀빌딩 201호</t>
+          <t>전북 전주시 덕진구 시천로 35 용진빌딩 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/welcomerebreed</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfasqmq</t>
+          <t>https://talk.naver.com/ct/wws0fj1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>409</v>
+        <v>147</v>
       </c>
       <c r="Q6" t="n">
-        <v>234</v>
+        <v>574</v>
       </c>
       <c r="R6" t="n">
-        <v>643</v>
+        <v>721</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,51 +1032,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2088657732</t>
+          <t>2051918606</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2088657732</t>
+          <t>https://m.place.naver.com/place/2051918606</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 효자점</t>
+          <t>리브리드 효자점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>welcomerebreed@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1399-8873</t>
+          <t>0507-1368-8931</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
+          <t>전북 전주시 완산구 홍산중앙로 13 돌핀빌딩 201호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223179008503</t>
+          <t>https://blog.naver.com/welcomerebreed</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ycz5</t>
+          <t>https://talk.naver.com/ct/wfasqmq</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1254</v>
+        <v>409</v>
       </c>
       <c r="Q7" t="n">
-        <v>423</v>
+        <v>234</v>
       </c>
       <c r="R7" t="n">
-        <v>1677</v>
+        <v>643</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,51 +1130,47 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1709963411</t>
+          <t>2088657732</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709963411</t>
+          <t>https://m.place.naver.com/place/2088657732</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>카이로짐 체형관리 PT샵 효천점</t>
+          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hyesungda@naver.com</t>
+          <t>onewayeco@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1415-5022</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
+          <t>전북 전주시 덕진구 화암4길 60 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/onewayfitness3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ftdy</t>
+          <t>https://talk.naver.com/ct/wwzxui7</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,17 +1205,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>68</v>
+        <v>1307</v>
       </c>
       <c r="Q8" t="n">
-        <v>76</v>
+        <v>331</v>
       </c>
       <c r="R8" t="n">
-        <v>144</v>
+        <v>1638</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1693804133</t>
+          <t>1857733969</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693804133</t>
+          <t>https://m.place.naver.com/place/1857733969</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1307,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q9" t="n">
         <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1332,7 +1328,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>하이짐 헬스&amp;PT 평화점</t>
+          <t>온탑피트니스 만성점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>higym_official@naver.com</t>
+          <t>ontopfit@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1375-7398</t>
+          <t>0507-1355-5810</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym_official</t>
+          <t>https://blog.naver.com/ontopfit</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,13 +1382,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4egfn</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>223</v>
+        <v>176</v>
       </c>
       <c r="Q10" t="n">
-        <v>79</v>
+        <v>280</v>
       </c>
       <c r="R10" t="n">
-        <v>302</v>
+        <v>456</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2060819661</t>
+          <t>1089561368</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060819661</t>
+          <t>https://m.place.naver.com/place/1089561368</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1438,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>온탑피트니스 만성점</t>
+          <t>하이짐 헬스&amp;PT 평화점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ontopfit@naver.com</t>
+          <t>higym_official@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1355-5810</t>
+          <t>0507-1375-7398</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ontopfit</t>
+          <t>https://blog.naver.com/higym_official</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1480,17 +1480,13 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4egfn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="Q11" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="R11" t="n">
-        <v>456</v>
+        <v>304</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1510,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1089561368</t>
+          <t>2060819661</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089561368</t>
+          <t>https://m.place.naver.com/place/2060819661</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/전주_PT.xlsx
+++ b/naver-place-crawler/results_health/전주_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,39 +564,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>카이로짐 체형관리 PT샵 효천점</t>
+          <t>짐플릭스 평화점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hyesungda@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1415-5022</t>
+          <t>0507-1408-8909</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
+          <t>전북 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ftdy</t>
+          <t>https://talk.naver.com/ct/wwx54rl</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>68</v>
+        <v>480</v>
       </c>
       <c r="Q2" t="n">
-        <v>76</v>
+        <v>884</v>
       </c>
       <c r="R2" t="n">
-        <v>144</v>
+        <v>1364</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1693804133</t>
+          <t>1336256244</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693804133</t>
+          <t>https://m.place.naver.com/place/1336256244</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐플릭스 평화점</t>
+          <t>짐플릭스 송천점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -673,18 +673,18 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1408-8909</t>
+          <t>0507-1382-8094</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 모악로 4678 7층</t>
+          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr/</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwx54rl</t>
+          <t>https://talk.naver.com/ct/w23okib</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>480</v>
+        <v>641</v>
       </c>
       <c r="Q3" t="n">
-        <v>884</v>
+        <v>862</v>
       </c>
       <c r="R3" t="n">
-        <v>1364</v>
+        <v>1503</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1336256244</t>
+          <t>1027880481</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336256244</t>
+          <t>https://m.place.naver.com/place/1027880481</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>짐플릭스 송천점</t>
+          <t>핑크팬더즈 삼천평화점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gymflix063@naver.com</t>
+          <t>pinkpandazym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1382-8094</t>
+          <t>0507-1351-9679</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://www.instagram.com/_pinkpandaz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w23okib</t>
+          <t>https://talk.naver.com/ct/w44lxq</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
       <c r="Q4" t="n">
-        <v>862</v>
+        <v>629</v>
       </c>
       <c r="R4" t="n">
-        <v>1501</v>
+        <v>1375</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1027880481</t>
+          <t>1302096727</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027880481</t>
+          <t>https://m.place.naver.com/place/1302096727</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>핑크팬더즈 삼천평화점 헬스&amp;PT</t>
+          <t>짐플릭스 송천2호점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pinkpandazym@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1351-9679</t>
+          <t>0507-1484-8094</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 안행로 9 2층 핑크팬더즈</t>
+          <t>전북 전주시 덕진구 시천로 35 용진빌딩 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_pinkpandaz</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44lxq</t>
+          <t>https://talk.naver.com/ct/wws0fj1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>745</v>
+        <v>147</v>
       </c>
       <c r="Q5" t="n">
-        <v>629</v>
+        <v>575</v>
       </c>
       <c r="R5" t="n">
-        <v>1374</v>
+        <v>722</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1302096727</t>
+          <t>2051918606</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302096727</t>
+          <t>https://m.place.naver.com/place/2051918606</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐플릭스 송천2호점</t>
+          <t>리브리드 효자점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymflix063@naver.com</t>
+          <t>welcomerebreed@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1484-8094</t>
+          <t>0507-1368-8931</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 시천로 35 용진빌딩 5층</t>
+          <t>전북 전주시 완산구 홍산중앙로 13 돌핀빌딩 201호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://blog.naver.com/welcomerebreed</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wws0fj1</t>
+          <t>https://talk.naver.com/ct/wfasqmq</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>147</v>
+        <v>409</v>
       </c>
       <c r="Q6" t="n">
-        <v>574</v>
+        <v>235</v>
       </c>
       <c r="R6" t="n">
-        <v>721</v>
+        <v>644</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2051918606</t>
+          <t>2088657732</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051918606</t>
+          <t>https://m.place.naver.com/place/2088657732</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1049,34 +1049,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>리브리드 효자점</t>
+          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>welcomerebreed@naver.com</t>
+          <t>onewayeco@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1368-8931</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산중앙로 13 돌핀빌딩 201호</t>
+          <t>전북 전주시 덕진구 화암4길 60 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/welcomerebreed</t>
+          <t>https://www.instagram.com/onewayfitness3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfasqmq</t>
+          <t>https://talk.naver.com/ct/wwzxui7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1107,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>409</v>
+        <v>1307</v>
       </c>
       <c r="Q7" t="n">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="R7" t="n">
-        <v>643</v>
+        <v>1638</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2088657732</t>
+          <t>1857733969</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2088657732</t>
+          <t>https://m.place.naver.com/place/1857733969</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,25 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
+          <t>24시 헬스 PT 제로백피트니스 효자점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>onewayeco@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1399-8873</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 화암4길 60 4층</t>
+          <t>전북 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onewayfitness3</t>
+          <t>https://blog.naver.com/zeroback2022/223179008503</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwzxui7</t>
+          <t>https://talk.naver.com/ct/w5ycz5</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1307</v>
+        <v>1255</v>
       </c>
       <c r="Q8" t="n">
-        <v>331</v>
+        <v>425</v>
       </c>
       <c r="R8" t="n">
-        <v>1638</v>
+        <v>1680</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1857733969</t>
+          <t>1709963411</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857733969</t>
+          <t>https://m.place.naver.com/place/1709963411</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,30 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>카이로짐 체형관리 PT샵 효천점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>hyesungda@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1415-5022</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
+          <t>https://talk.naver.com/ct/w4ftdy</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>264</v>
+        <v>68</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="R9" t="n">
-        <v>291</v>
+        <v>144</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>1693804133</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/1693804133</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,34 +1344,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>온탑피트니스 만성점</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ontopfit@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1355-5810</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ontopfit</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4egfn</t>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>176</v>
+        <v>266</v>
       </c>
       <c r="Q10" t="n">
-        <v>280</v>
+        <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>456</v>
+        <v>293</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1089561368</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089561368</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>하이짐 헬스&amp;PT 평화점</t>
+          <t>온탑피트니스 만성점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>higym_official@naver.com</t>
+          <t>ontopfit@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1375-7398</t>
+          <t>0507-1355-5810</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym_official</t>
+          <t>https://blog.naver.com/ontopfit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1480,13 +1480,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4egfn</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1495,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="Q11" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="R11" t="n">
-        <v>304</v>
+        <v>456</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2060819661</t>
+          <t>1089561368</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060819661</t>
+          <t>https://m.place.naver.com/place/1089561368</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
